--- a/data/lineup.xlsx
+++ b/data/lineup.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:K79"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,6 +430,9 @@
       <c r="J1" t="str">
         <v>instagram</v>
       </c>
+      <c r="K1" t="str">
+        <v>display_category_label</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1123,7 +1126,7 @@
         <v>library</v>
       </c>
       <c r="G23" t="str">
-        <v>All day</v>
+        <v>11:00-15:30</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1133,6 +1136,9 @@
       </c>
       <c r="J23" t="str">
         <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>activity</v>
       </c>
     </row>
     <row r="24">
@@ -1283,7 +1289,7 @@
         <v>library</v>
       </c>
       <c r="G28" t="str">
-        <v>All day</v>
+        <v>10:00-13:00</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -2449,25 +2455,25 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>up-rooted</v>
+        <v>lego-club</v>
       </c>
       <c r="B65" t="str">
-        <v>Up Rooted</v>
+        <v>Lego Club</v>
       </c>
       <c r="C65" t="str">
-        <v>Poetry anthology written by Nottingham school children — a Green Hustle project.</v>
+        <v>Free-range Lego building for all ages from Nottingham's local Lego club.</v>
       </c>
       <c r="D65" t="str">
-        <v>Up Rooted is Green Hustle's internal poetry anthology, written by school children across Nottingham. A celebration of young voices on themes of nature, growing, climate and community — published for the festival.</v>
+        <v>Nottingham's local Lego club — pull up a chair and build whatever you like with a giant shared pile of Lego. No instructions, no projects — just open building for all ages.</v>
       </c>
       <c r="E65" t="str">
-        <v>talks</v>
+        <v>workshops</v>
       </c>
       <c r="F65" t="str">
         <v>library</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>10:00-14:00</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -2481,22 +2487,22 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>lego-club</v>
+        <v>shifting-your-mindset</v>
       </c>
       <c r="B66" t="str">
-        <v>Lego Club</v>
+        <v>Shifting Your Mindset</v>
       </c>
       <c r="C66" t="str">
-        <v>Free-range Lego building for all ages from Nottingham's local Lego club.</v>
+        <v/>
       </c>
       <c r="D66" t="str">
-        <v>Nottingham's local Lego club — pull up a chair and build whatever you like with a giant shared pile of Lego. No instructions, no projects — just open building for all ages.</v>
+        <v/>
       </c>
       <c r="E66" t="str">
-        <v>workshops</v>
+        <v>markets</v>
       </c>
       <c r="F66" t="str">
-        <v>library</v>
+        <v>market</v>
       </c>
       <c r="G66" t="str">
         <v>All day</v>
@@ -2505,7 +2511,7 @@
         <v/>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>www.shiftingyourmindset.co.uk</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -2513,10 +2519,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>shifting-your-mindset</v>
+        <v>children-as-researchers</v>
       </c>
       <c r="B67" t="str">
-        <v>Shifting Your Mindset</v>
+        <v>Children as Researchers</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -2525,7 +2531,7 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>markets</v>
+        <v>workshops</v>
       </c>
       <c r="F67" t="str">
         <v>market</v>
@@ -2537,7 +2543,7 @@
         <v/>
       </c>
       <c r="I67" t="str">
-        <v>www.shiftingyourmindset.co.uk</v>
+        <v/>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -2545,10 +2551,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>children-as-researchers</v>
+        <v>dished</v>
       </c>
       <c r="B68" t="str">
-        <v>Children as Researchers</v>
+        <v>DISHED</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -2557,7 +2563,7 @@
         <v/>
       </c>
       <c r="E68" t="str">
-        <v>workshops</v>
+        <v>food</v>
       </c>
       <c r="F68" t="str">
         <v>market</v>
@@ -2569,7 +2575,7 @@
         <v/>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>https://www.ids.ac.uk/projects/dished</v>
       </c>
       <c r="J68" t="str">
         <v/>
@@ -2577,10 +2583,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>dished</v>
+        <v>nottingham-food-charter-action-cafe</v>
       </c>
       <c r="B69" t="str">
-        <v>DISHED</v>
+        <v>Nottingham Food Charter Action Cafe</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -2589,19 +2595,19 @@
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>food</v>
+        <v>talks</v>
       </c>
       <c r="F69" t="str">
         <v>market</v>
       </c>
       <c r="G69" t="str">
-        <v>All day</v>
+        <v/>
       </c>
       <c r="H69" t="str">
         <v/>
       </c>
       <c r="I69" t="str">
-        <v>https://www.ids.ac.uk/projects/dished</v>
+        <v/>
       </c>
       <c r="J69" t="str">
         <v/>
@@ -2609,10 +2615,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>nottingham-food-charter-action-cafe</v>
+        <v>library-of-no-returns</v>
       </c>
       <c r="B70" t="str">
-        <v>Nottingham Food Charter Action Cafe</v>
+        <v>Library of No Returns</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -2621,7 +2627,7 @@
         <v/>
       </c>
       <c r="E70" t="str">
-        <v>talks</v>
+        <v>markets</v>
       </c>
       <c r="F70" t="str">
         <v>market</v>
@@ -2641,10 +2647,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>library-of-no-returns</v>
+        <v>nottingham-growing-network</v>
       </c>
       <c r="B71" t="str">
-        <v>Library of No Returns</v>
+        <v>Nottingham Growing Network</v>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -2665,7 +2671,7 @@
         <v/>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>nottinghamgrowingnetwork.org</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -2673,10 +2679,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>nottingham-growing-network</v>
+        <v>city-local-group-walks</v>
       </c>
       <c r="B72" t="str">
-        <v>Nottingham Growing Network</v>
+        <v>City Local Group Walks</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -2685,10 +2691,10 @@
         <v/>
       </c>
       <c r="E72" t="str">
-        <v>markets</v>
+        <v>talks</v>
       </c>
       <c r="F72" t="str">
-        <v>market</v>
+        <v/>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -2697,7 +2703,7 @@
         <v/>
       </c>
       <c r="I72" t="str">
-        <v>nottinghamgrowingnetwork.org</v>
+        <v/>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -2705,10 +2711,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>city-local-group-walks</v>
+        <v>rights-for-flies</v>
       </c>
       <c r="B73" t="str">
-        <v>City Local Group Walks</v>
+        <v>Rights for Flies</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -2717,10 +2723,10 @@
         <v/>
       </c>
       <c r="E73" t="str">
-        <v>talks</v>
+        <v>markets</v>
       </c>
       <c r="F73" t="str">
-        <v/>
+        <v>market</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -2729,56 +2735,56 @@
         <v/>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>www.rightsforflies.com</v>
       </c>
       <c r="J73" t="str">
-        <v/>
+        <v>@rights4flies</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>rights-for-flies</v>
+        <v>natalie-hunt-vegetable-woman</v>
       </c>
       <c r="B74" t="str">
-        <v>Rights for Flies</v>
+        <v>Natalie Hunt: The Vegetable Woman</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>Walkabout performer in elaborate vegetable costume.</v>
       </c>
       <c r="D74" t="str">
-        <v/>
+        <v>A walkabout performance bringing the eccentricity of homegrown vegetables to life around the market square.</v>
       </c>
       <c r="E74" t="str">
-        <v>markets</v>
+        <v>music</v>
       </c>
       <c r="F74" t="str">
         <v>market</v>
       </c>
       <c r="G74" t="str">
-        <v/>
+        <v>All day</v>
       </c>
       <c r="H74" t="str">
         <v/>
       </c>
       <c r="I74" t="str">
-        <v>www.rightsforflies.com</v>
+        <v/>
       </c>
       <c r="J74" t="str">
-        <v>@rights4flies</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>natalie-hunt-vegetable-woman</v>
+        <v>karen-stilts</v>
       </c>
       <c r="B75" t="str">
-        <v>Natalie Hunt: The Vegetable Woman</v>
+        <v>Karen Stilts</v>
       </c>
       <c r="C75" t="str">
-        <v>Walkabout performer in elaborate vegetable costume.</v>
+        <v>Stilt-walking performer roaming the square.</v>
       </c>
       <c r="D75" t="str">
-        <v>A walkabout performance bringing the eccentricity of homegrown vegetables to life around the market square.</v>
+        <v>A roving stilt-walking performer adding height and spectacle to Old Market Square throughout the day.</v>
       </c>
       <c r="E75" t="str">
         <v>music</v>
@@ -2801,19 +2807,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>karen-stilts</v>
+        <v>sprout-n-about</v>
       </c>
       <c r="B76" t="str">
-        <v>Karen Stilts</v>
+        <v>Sprout N About</v>
       </c>
       <c r="C76" t="str">
-        <v>Stilt-walking performer roaming the square.</v>
+        <v>A growing project running alongside Rights For Flies.</v>
       </c>
       <c r="D76" t="str">
-        <v>A roving stilt-walking performer adding height and spectacle to Old Market Square throughout the day.</v>
+        <v/>
       </c>
       <c r="E76" t="str">
-        <v>music</v>
+        <v>markets</v>
       </c>
       <c r="F76" t="str">
         <v>market</v>
@@ -2833,19 +2839,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>sprout-n-about</v>
+        <v>nottingham-playhouse</v>
       </c>
       <c r="B77" t="str">
-        <v>Sprout N About</v>
+        <v>Nottingham Playhouse</v>
       </c>
       <c r="C77" t="str">
-        <v>A growing project running alongside Rights For Flies.</v>
+        <v/>
       </c>
       <c r="D77" t="str">
         <v/>
       </c>
       <c r="E77" t="str">
-        <v>markets</v>
+        <v>talks</v>
       </c>
       <c r="F77" t="str">
         <v>market</v>
@@ -2857,7 +2863,7 @@
         <v/>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>https://nottinghamplayhouse.co.uk/</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -2865,10 +2871,10 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>nottingham-playhouse</v>
+        <v>octopode-emporium</v>
       </c>
       <c r="B78" t="str">
-        <v>Nottingham Playhouse</v>
+        <v>The Octopode Emporium</v>
       </c>
       <c r="C78" t="str">
         <v/>
@@ -2877,7 +2883,7 @@
         <v/>
       </c>
       <c r="E78" t="str">
-        <v>talks</v>
+        <v>markets</v>
       </c>
       <c r="F78" t="str">
         <v>market</v>
@@ -2889,7 +2895,7 @@
         <v/>
       </c>
       <c r="I78" t="str">
-        <v>https://nottinghamplayhouse.co.uk/</v>
+        <v/>
       </c>
       <c r="J78" t="str">
         <v/>
@@ -2897,10 +2903,10 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>octopode-emporium</v>
+        <v>yoga-sussex</v>
       </c>
       <c r="B79" t="str">
-        <v>The Octopode Emporium</v>
+        <v>Yoga</v>
       </c>
       <c r="C79" t="str">
         <v/>
@@ -2909,13 +2915,13 @@
         <v/>
       </c>
       <c r="E79" t="str">
-        <v>markets</v>
+        <v>workshops</v>
       </c>
       <c r="F79" t="str">
-        <v>market</v>
+        <v>sussex</v>
       </c>
       <c r="G79" t="str">
-        <v>All day</v>
+        <v/>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -2924,44 +2930,12 @@
         <v/>
       </c>
       <c r="J79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>yoga-sussex</v>
-      </c>
-      <c r="B80" t="str">
-        <v>Yoga</v>
-      </c>
-      <c r="C80" t="str">
-        <v/>
-      </c>
-      <c r="D80" t="str">
-        <v/>
-      </c>
-      <c r="E80" t="str">
-        <v>workshops</v>
-      </c>
-      <c r="F80" t="str">
-        <v>sussex</v>
-      </c>
-      <c r="G80" t="str">
-        <v/>
-      </c>
-      <c r="H80" t="str">
-        <v/>
-      </c>
-      <c r="I80" t="str">
-        <v/>
-      </c>
-      <c r="J80" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J80"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K79"/>
   </ignoredErrors>
 </worksheet>
 </file>